--- a/exports/DLF_full_report.xlsx
+++ b/exports/DLF_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:U80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>5.73</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>407.4</v>
+        <v>401.55</v>
       </c>
       <c r="I2" t="n">
         <v>401.9233298654538</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.31</v>
+        <v>-1.74</v>
       </c>
       <c r="L2" t="n">
         <v>3.87</v>
       </c>
       <c r="M2" t="n">
-        <v>0.73</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
         <v>4.26</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>6.86</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>387.5</v>
+        <v>407.9</v>
       </c>
       <c r="I3" t="n">
         <v>402.2787963366202</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>-1.58</v>
       </c>
       <c r="L3" t="n">
-        <v>1.02</v>
+        <v>1.61</v>
       </c>
       <c r="M3" t="n">
         <v>0.74</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>11.71</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>377.5</v>
+        <v>367.7</v>
       </c>
       <c r="I4" t="n">
         <v>370.4216943714475</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.45</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>7.69</v>
+        <v>10.76</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>2.03</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>6.49</v>
       </c>
       <c r="O4" t="n">
         <v>4.08</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.84</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>339.6</v>
+        <v>357</v>
       </c>
       <c r="I5" t="n">
         <v>345.3581552754693</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>7.64</v>
+        <v>2.91</v>
       </c>
       <c r="L5" t="n">
         <v>2.28</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.23</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>386.25</v>
+        <v>373.8</v>
       </c>
       <c r="I6" t="n">
         <v>379.9027816971713</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>8.19</v>
+        <v>4.71</v>
       </c>
       <c r="L6" t="n">
         <v>6.05</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>8.85</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>323</v>
+        <v>344.95</v>
       </c>
       <c r="I7" t="n">
         <v>340.3300916832018</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>38</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>13.59</v>
+        <v>7.72</v>
       </c>
       <c r="L7" t="n">
         <v>4.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="N7" t="n">
-        <v>4.56</v>
+        <v>7.43</v>
       </c>
       <c r="O7" t="n">
         <v>-3.67</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>12.22</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44718.55208333334</v>
+        <v>44719.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>326</v>
+        <v>317.45</v>
       </c>
       <c r="I8" t="n">
         <v>318.0929441512088</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.49</v>
+        <v>-7.97</v>
       </c>
       <c r="L8" t="n">
-        <v>6.35</v>
+        <v>8.65</v>
       </c>
       <c r="M8" t="n">
         <v>0.44</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.77</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44743.38541666666</v>
+        <v>44743.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>321.6</v>
+        <v>323</v>
       </c>
       <c r="I9" t="n">
         <v>322.2408495568635</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.31</v>
+        <v>-1.75</v>
       </c>
       <c r="L9" t="n">
         <v>4.44</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.45</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44776.55208333334</v>
+        <v>44777.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>372.3</v>
+        <v>366</v>
       </c>
       <c r="I10" t="n">
         <v>367.9621768726478</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K10" t="n">
-        <v>15.26</v>
+        <v>13.31</v>
       </c>
       <c r="L10" t="n">
         <v>1.5</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>7.46</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44803.38541666666</v>
+        <v>44803.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>385.1</v>
+        <v>389.85</v>
       </c>
       <c r="I11" t="n">
         <v>386.3797198126883</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.22</v>
+        <v>-6.52</v>
       </c>
       <c r="L11" t="n">
-        <v>6.83</v>
+        <v>7.1</v>
       </c>
       <c r="M11" t="n">
         <v>0.92</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>6.29</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44820.38541666666</v>
+        <v>44820.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>397.05</v>
+        <v>387</v>
       </c>
       <c r="I12" t="n">
         <v>387.9467784299127</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>1.85</v>
+        <v>-0.73</v>
       </c>
       <c r="L12" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
         <v>1.97</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.65</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44859.55208333334</v>
+        <v>44861.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>369.7</v>
+        <v>379.95</v>
       </c>
       <c r="I13" t="n">
         <v>375.8632835991123</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>39</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K13" t="n">
-        <v>4.47</v>
+        <v>1.82</v>
       </c>
       <c r="L13" t="n">
         <v>3.4</v>
@@ -1182,7 +1337,7 @@
         <v>1.72</v>
       </c>
       <c r="N13" t="n">
-        <v>3.19</v>
+        <v>3.92</v>
       </c>
       <c r="O13" t="n">
         <v>-5.48</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.03</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44910.55208333334</v>
+        <v>44911.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>398.8</v>
+        <v>396.8</v>
       </c>
       <c r="I14" t="n">
         <v>398.5056613685064</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K14" t="n">
-        <v>4.96</v>
+        <v>4.43</v>
       </c>
       <c r="L14" t="n">
         <v>2.7</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.18</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44972.55208333334</v>
+        <v>44973.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>361.15</v>
+        <v>371.7</v>
       </c>
       <c r="I15" t="n">
         <v>369.1824853818125</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K15" t="n">
-        <v>8.98</v>
+        <v>6.33</v>
       </c>
       <c r="L15" t="n">
         <v>1.39</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.76</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>356.7</v>
+        <v>349.45</v>
       </c>
       <c r="I16" t="n">
         <v>351.9039567490671</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.04</v>
+        <v>-5.99</v>
       </c>
       <c r="L16" t="n">
-        <v>4.22</v>
+        <v>6.63</v>
       </c>
       <c r="M16" t="n">
         <v>0.24</v>
       </c>
       <c r="N16" t="n">
-        <v>1.99</v>
+        <v>2.48</v>
       </c>
       <c r="O16" t="n">
         <v>2.67</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.28</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44991.55208333334</v>
+        <v>44993.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>359.5</v>
+        <v>360.9</v>
       </c>
       <c r="I17" t="n">
         <v>360.7674992998624</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.88</v>
+        <v>-3.28</v>
       </c>
       <c r="L17" t="n">
         <v>4.28</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>5.15</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>349.3</v>
+        <v>342</v>
       </c>
       <c r="I18" t="n">
         <v>347.433656525373</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.21</v>
+        <v>-5.24</v>
       </c>
       <c r="L18" t="n">
-        <v>3.66</v>
+        <v>5.43</v>
       </c>
       <c r="M18" t="n">
         <v>0.59</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.76</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45001.38541666666</v>
+        <v>45001.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>359.25</v>
+        <v>361</v>
       </c>
       <c r="I19" t="n">
         <v>359.3790595357493</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.04</v>
+        <v>-5.56</v>
       </c>
       <c r="L19" t="n">
-        <v>5.44</v>
+        <v>5.69</v>
       </c>
       <c r="M19" t="n">
         <v>1.6</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>5.74</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45012.38541666666</v>
+        <v>45012.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>351.75</v>
+        <v>348.75</v>
       </c>
       <c r="I20" t="n">
         <v>351.4601214841356</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.56</v>
+        <v>-3.39</v>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="M20" t="n">
         <v>0.16</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.82</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>361</v>
+        <v>366.6</v>
       </c>
       <c r="I21" t="n">
         <v>366.5778123473121</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.51</v>
+        <v>-5.12</v>
       </c>
       <c r="L21" t="n">
-        <v>4.13</v>
+        <v>6.24</v>
       </c>
       <c r="M21" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="O21" t="n">
         <v>-1.39</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.98</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45098.55208333334</v>
+        <v>45099.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>483</v>
+        <v>480.55</v>
       </c>
       <c r="I22" t="n">
         <v>482.8684656207878</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>77.16666666666667</v>
+        <v>78</v>
       </c>
       <c r="K22" t="n">
-        <v>31.75</v>
+        <v>31.08</v>
       </c>
       <c r="L22" t="n">
         <v>1.43</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>4.76</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45111.55208333334</v>
+        <v>45112.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>489.4</v>
+        <v>495.45</v>
       </c>
       <c r="I23" t="n">
         <v>494.5976752244737</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.84</v>
+        <v>-3.1</v>
       </c>
       <c r="L23" t="n">
         <v>3.63</v>
@@ -1752,7 +2027,7 @@
         <v>0.73</v>
       </c>
       <c r="N23" t="n">
-        <v>1.23</v>
+        <v>2.93</v>
       </c>
       <c r="O23" t="n">
         <v>-0.62</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>4.61</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45118.55208333334</v>
+        <v>45119.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>499</v>
+        <v>492.2</v>
       </c>
       <c r="I24" t="n">
         <v>492.4831628548388</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="M24" t="n">
         <v>0.03</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>4.94</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45134.38541666666</v>
+        <v>45134.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="I25" t="n">
         <v>505.4975338393257</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.4</v>
+        <v>-3.82</v>
       </c>
       <c r="L25" t="n">
-        <v>3.41</v>
+        <v>4.39</v>
       </c>
       <c r="M25" t="n">
         <v>0.61</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>6.1</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>499.7</v>
+        <v>486.95</v>
       </c>
       <c r="I26" t="n">
         <v>491.022055395305</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.21</v>
+        <v>-4.71</v>
       </c>
       <c r="L26" t="n">
-        <v>2.76</v>
+        <v>4.96</v>
       </c>
       <c r="M26" t="n">
         <v>1.51</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.84</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45166.55208333334</v>
+        <v>45167.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>481.9</v>
+        <v>496.3</v>
       </c>
       <c r="I27" t="n">
         <v>494.3991165191781</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K27" t="n">
-        <v>1.04</v>
+        <v>-1.92</v>
       </c>
       <c r="L27" t="n">
         <v>3.29</v>
@@ -1980,7 +2303,7 @@
         <v>0.7</v>
       </c>
       <c r="N27" t="n">
-        <v>1.61</v>
+        <v>2.61</v>
       </c>
       <c r="O27" t="n">
         <v>-1.18</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>5.8</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>522.75</v>
+        <v>513.4</v>
       </c>
       <c r="I28" t="n">
         <v>520.0709923355827</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K28" t="n">
-        <v>5.33</v>
+        <v>3.45</v>
       </c>
       <c r="L28" t="n">
         <v>2.68</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.84</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45205.38541666666</v>
+        <v>45205.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>532.05</v>
+        <v>548.3</v>
       </c>
       <c r="I29" t="n">
         <v>540.4010364993782</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.63</v>
+        <v>-6.8</v>
       </c>
       <c r="L29" t="n">
-        <v>5.36</v>
+        <v>7.23</v>
       </c>
       <c r="M29" t="n">
         <v>0.57</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.56</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>551.1</v>
+        <v>538.1</v>
       </c>
       <c r="I30" t="n">
         <v>545.1201595383554</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>0.51</v>
+        <v>-1.86</v>
       </c>
       <c r="L30" t="n">
         <v>3.02</v>
@@ -2151,7 +2510,7 @@
         <v>0.77</v>
       </c>
       <c r="N30" t="n">
-        <v>1.8</v>
+        <v>3.47</v>
       </c>
       <c r="O30" t="n">
         <v>4.44</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.7</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45226.55208333334</v>
+        <v>45229.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>536</v>
+        <v>551.95</v>
       </c>
       <c r="I31" t="n">
         <v>550.7622162184755</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.39</v>
+        <v>-2.57</v>
       </c>
       <c r="L31" t="n">
         <v>3.26</v>
@@ -2208,7 +2579,7 @@
         <v>0.61</v>
       </c>
       <c r="N31" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="O31" t="n">
         <v>-3.47</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.89</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>775.6</v>
+        <v>751.15</v>
       </c>
       <c r="I32" t="n">
         <v>768.5147239980836</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>82.16666666666667</v>
+        <v>85</v>
       </c>
       <c r="K32" t="n">
-        <v>40.52</v>
+        <v>36.09</v>
       </c>
       <c r="L32" t="n">
         <v>3.75</v>
@@ -2265,7 +2648,7 @@
         <v>0.91</v>
       </c>
       <c r="N32" t="n">
-        <v>3.46</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
         <v>3.96</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="I33" t="n">
         <v>790.850751546854</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.24</v>
+        <v>-6.24</v>
       </c>
       <c r="L33" t="n">
-        <v>6.33</v>
+        <v>6.83</v>
       </c>
       <c r="M33" t="n">
         <v>4.08</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.92</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>909.35</v>
+        <v>872.55</v>
       </c>
       <c r="I34" t="n">
         <v>885.5214916137363</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K34" t="n">
-        <v>13.95</v>
+        <v>9.34</v>
       </c>
       <c r="L34" t="n">
         <v>1.94</v>
@@ -2379,7 +2786,7 @@
         <v>1.38</v>
       </c>
       <c r="N34" t="n">
-        <v>2.84</v>
+        <v>4.93</v>
       </c>
       <c r="O34" t="n">
         <v>1.79</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.49</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>874</v>
+        <v>884.6</v>
       </c>
       <c r="I35" t="n">
         <v>880.5980819329035</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.17</v>
+        <v>-1.38</v>
       </c>
       <c r="L35" t="n">
         <v>4.9</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.72</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45385.55208333334</v>
+        <v>45386.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>903.55</v>
+        <v>889.2</v>
       </c>
       <c r="I36" t="n">
         <v>889.655362779141</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K36" t="n">
-        <v>2.14</v>
+        <v>0.52</v>
       </c>
       <c r="L36" t="n">
         <v>1.02</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.64</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>895.15</v>
+        <v>903.5</v>
       </c>
       <c r="I37" t="n">
         <v>897.6780251935058</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.67</v>
+        <v>-1.61</v>
       </c>
       <c r="L37" t="n">
         <v>4.66</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>5.28</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>885.8</v>
+        <v>845.45</v>
       </c>
       <c r="I38" t="n">
         <v>864.4291691394403</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.96</v>
+        <v>-6.43</v>
       </c>
       <c r="L38" t="n">
-        <v>4.5</v>
+        <v>6.95</v>
       </c>
       <c r="M38" t="n">
         <v>0.48</v>
       </c>
       <c r="N38" t="n">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="O38" t="n">
         <v>1.52</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>10.23</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>822.4</v>
+        <v>852.25</v>
       </c>
       <c r="I39" t="n">
         <v>845.0731920349488</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K39" t="n">
-        <v>2.73</v>
+        <v>-0.8</v>
       </c>
       <c r="L39" t="n">
         <v>5.86</v>
       </c>
       <c r="M39" t="n">
-        <v>1.19</v>
+        <v>4.07</v>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>5.67</v>
       </c>
       <c r="O39" t="n">
         <v>-3.4</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.23</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>869</v>
+        <v>762.65</v>
       </c>
       <c r="I40" t="n">
         <v>812.8474087058701</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1.97</v>
+        <v>-10.51</v>
       </c>
       <c r="L40" t="n">
-        <v>2.02</v>
+        <v>19.38</v>
       </c>
       <c r="M40" t="n">
         <v>-0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="O40" t="n">
         <v>5.67</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>16.1</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45455.55208333334</v>
+        <v>45456.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>858.05</v>
+        <v>873.6</v>
       </c>
       <c r="I41" t="n">
         <v>871.4478489482452</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K41" t="n">
-        <v>-12.51</v>
+        <v>-14.55</v>
       </c>
       <c r="L41" t="n">
-        <v>15.39</v>
+        <v>15.45</v>
       </c>
       <c r="M41" t="n">
         <v>1.37</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.92</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45467.55208333334</v>
+        <v>45468.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>839</v>
+        <v>815.8</v>
       </c>
       <c r="I42" t="n">
         <v>830.9680459215622</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.96</v>
+        <v>-6.62</v>
       </c>
       <c r="L42" t="n">
-        <v>4.59</v>
+        <v>6.79</v>
       </c>
       <c r="M42" t="n">
         <v>0.67</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>7.91</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45499.55208333334</v>
+        <v>45502.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>828</v>
+        <v>869.05</v>
       </c>
       <c r="I43" t="n">
         <v>855.8003141965779</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.5</v>
+        <v>-6.53</v>
       </c>
       <c r="L43" t="n">
-        <v>4.56</v>
+        <v>7.38</v>
       </c>
       <c r="M43" t="n">
         <v>0.79</v>
       </c>
       <c r="N43" t="n">
-        <v>2.19</v>
+        <v>4.92</v>
       </c>
       <c r="O43" t="n">
         <v>-1.55</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.69</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>841.45</v>
+        <v>811.1</v>
       </c>
       <c r="I44" t="n">
         <v>834.3215019966754</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.18</v>
+        <v>-6.67</v>
       </c>
       <c r="L44" t="n">
-        <v>4.44</v>
+        <v>7.9</v>
       </c>
       <c r="M44" t="n">
         <v>1.6</v>
       </c>
       <c r="N44" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O44" t="n">
         <v>4.92</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45520.38541666666</v>
+        <v>45520.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>861.1</v>
+        <v>866.2</v>
       </c>
       <c r="I45" t="n">
         <v>863.362861436942</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.16</v>
+        <v>-6.79</v>
       </c>
       <c r="L45" t="n">
-        <v>6.4</v>
+        <v>7.75</v>
       </c>
       <c r="M45" t="n">
         <v>3.77</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>5.81</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>841.5</v>
+        <v>813.2</v>
       </c>
       <c r="I46" t="n">
         <v>825.043839394581</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.85</v>
+        <v>-6.12</v>
       </c>
       <c r="L46" t="n">
-        <v>5.51</v>
+        <v>6.54</v>
       </c>
       <c r="M46" t="n">
         <v>0.86</v>
       </c>
       <c r="N46" t="n">
-        <v>1.33</v>
+        <v>3.24</v>
       </c>
       <c r="O46" t="n">
         <v>5.47</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>6.2</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45547.55208333334</v>
+        <v>45548.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>834.9</v>
+        <v>862</v>
       </c>
       <c r="I47" t="n">
         <v>849.4989853571828</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.67</v>
+        <v>-6</v>
       </c>
       <c r="L47" t="n">
-        <v>3.42</v>
+        <v>6.1</v>
       </c>
       <c r="M47" t="n">
         <v>0.61</v>
       </c>
       <c r="N47" t="n">
-        <v>1.52</v>
+        <v>3.72</v>
       </c>
       <c r="O47" t="n">
         <v>-3.24</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>912.55</v>
+        <v>867.05</v>
       </c>
       <c r="I48" t="n">
         <v>867.8775193806612</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>5.86</v>
+        <v>0.59</v>
       </c>
       <c r="L48" t="n">
         <v>3.33</v>
       </c>
       <c r="M48" t="n">
-        <v>0.55</v>
+        <v>2.64</v>
       </c>
       <c r="N48" t="n">
-        <v>2.14</v>
+        <v>5.56</v>
       </c>
       <c r="O48" t="n">
         <v>3.72</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45593.55208333334</v>
+        <v>45594.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>821.55</v>
+        <v>834.3</v>
       </c>
       <c r="I49" t="n">
         <v>830.432068855317</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>5.25</v>
+        <v>3.78</v>
       </c>
       <c r="L49" t="n">
         <v>4.72</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>8.69</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45608.38541666666</v>
+        <v>45608.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>775.15</v>
+        <v>763.45</v>
       </c>
       <c r="I50" t="n">
         <v>774.6809519116239</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-7.09</v>
+        <v>-8.49</v>
       </c>
       <c r="L50" t="n">
-        <v>7.49</v>
+        <v>8.65</v>
       </c>
       <c r="M50" t="n">
         <v>0.36</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>6.9</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45617.55208333334</v>
+        <v>45618.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>776</v>
+        <v>806.1</v>
       </c>
       <c r="I51" t="n">
         <v>797.2328831287775</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.64</v>
+        <v>-5.59</v>
       </c>
       <c r="L51" t="n">
-        <v>2.36</v>
+        <v>5.92</v>
       </c>
       <c r="M51" t="n">
         <v>2.26</v>
       </c>
       <c r="N51" t="n">
-        <v>2.11</v>
+        <v>3.54</v>
       </c>
       <c r="O51" t="n">
         <v>-1.91</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>863</v>
+        <v>846.6</v>
       </c>
       <c r="I52" t="n">
         <v>853.8684992231789</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K52" t="n">
-        <v>7.06</v>
+        <v>5.02</v>
       </c>
       <c r="L52" t="n">
         <v>3.75</v>
@@ -3405,7 +4028,7 @@
         <v>1.29</v>
       </c>
       <c r="N52" t="n">
-        <v>2.03</v>
+        <v>3.88</v>
       </c>
       <c r="O52" t="n">
         <v>3.54</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.11</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45686.55208333334</v>
+        <v>45687.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>745.3</v>
+        <v>758.95</v>
       </c>
       <c r="I53" t="n">
         <v>746.7838747300603</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K53" t="n">
-        <v>11.97</v>
+        <v>10.35</v>
       </c>
       <c r="L53" t="n">
         <v>2.73</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>7.47</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>729.5</v>
+        <v>706.05</v>
       </c>
       <c r="I54" t="n">
         <v>726.7255311334484</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.88</v>
+        <v>-6.97</v>
       </c>
       <c r="L54" t="n">
-        <v>4.11</v>
+        <v>6.98</v>
       </c>
       <c r="M54" t="n">
         <v>0.62</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.09</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45734.38541666666</v>
+        <v>45734.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>672.2</v>
+        <v>676.75</v>
       </c>
       <c r="I55" t="n">
         <v>674.5104667668309</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>4.79</v>
+        <v>4.15</v>
       </c>
       <c r="L55" t="n">
         <v>3.46</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>6.44</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>680</v>
+        <v>662.15</v>
       </c>
       <c r="I56" t="n">
         <v>668.0306823759526</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>10</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>0.48</v>
+        <v>-2.16</v>
       </c>
       <c r="L56" t="n">
-        <v>0.99</v>
+        <v>3.46</v>
       </c>
       <c r="M56" t="n">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="N56" t="n">
-        <v>2.08</v>
+        <v>2.57</v>
       </c>
       <c r="O56" t="n">
         <v>3.13</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.35</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>657.15</v>
+        <v>663</v>
       </c>
       <c r="I57" t="n">
         <v>662.0940104179679</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>0.76</v>
+        <v>-0.13</v>
       </c>
       <c r="L57" t="n">
         <v>4.46</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>8.35</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>676.1</v>
+        <v>650</v>
       </c>
       <c r="I58" t="n">
         <v>654.0131754947479</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K58" t="n">
-        <v>1.98</v>
+        <v>-1.96</v>
       </c>
       <c r="L58" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="M58" t="n">
         <v>0.64</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45790.55208333334</v>
+        <v>45791.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>679</v>
+        <v>691.05</v>
       </c>
       <c r="I59" t="n">
         <v>681.3166805370355</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.46</v>
+        <v>-6.32</v>
       </c>
       <c r="L59" t="n">
-        <v>5.37</v>
+        <v>7.57</v>
       </c>
       <c r="M59" t="n">
         <v>3.23</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.49</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45839.55208333334</v>
+        <v>45840.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>844</v>
+        <v>830.2</v>
       </c>
       <c r="I60" t="n">
         <v>833.4658367323252</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K60" t="n">
-        <v>22.13</v>
+        <v>20.14</v>
       </c>
       <c r="L60" t="n">
         <v>1.99</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.96</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45856.55208333334</v>
+        <v>45859.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>842.85</v>
+        <v>849.8</v>
       </c>
       <c r="I61" t="n">
         <v>848.7329123514601</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.52</v>
+        <v>-2.36</v>
       </c>
       <c r="L61" t="n">
         <v>3.11</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>4.38</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>824</v>
+        <v>793.3</v>
       </c>
       <c r="I62" t="n">
         <v>818.9524602464652</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.04</v>
+        <v>-6.65</v>
       </c>
       <c r="L62" t="n">
-        <v>3.22</v>
+        <v>6.8</v>
       </c>
       <c r="M62" t="n">
-        <v>0.02</v>
+        <v>0.61</v>
       </c>
       <c r="N62" t="n">
-        <v>1.46</v>
+        <v>4.64</v>
       </c>
       <c r="O62" t="n">
         <v>1.2</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.69</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45912.55208333334</v>
+        <v>45915.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>757.5</v>
+        <v>777.3</v>
       </c>
       <c r="I63" t="n">
         <v>773.3688523795904</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K63" t="n">
-        <v>4.51</v>
+        <v>2.02</v>
       </c>
       <c r="L63" t="n">
         <v>3.42</v>
@@ -4032,7 +4787,7 @@
         <v>2.09</v>
       </c>
       <c r="N63" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="O63" t="n">
         <v>-4.64</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5.05</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>760.3</v>
+        <v>741.25</v>
       </c>
       <c r="I64" t="n">
         <v>756.7391700377016</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.19</v>
+        <v>-4.64</v>
       </c>
       <c r="L64" t="n">
-        <v>2.73</v>
+        <v>5.28</v>
       </c>
       <c r="M64" t="n">
-        <v>0.12</v>
+        <v>0.43</v>
       </c>
       <c r="N64" t="n">
-        <v>1.77</v>
+        <v>3.49</v>
       </c>
       <c r="O64" t="n">
         <v>2.46</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.1</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>741.1</v>
+        <v>761.9</v>
       </c>
       <c r="I65" t="n">
         <v>742.7241289844841</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K65" t="n">
-        <v>0.02</v>
+        <v>-2.79</v>
       </c>
       <c r="L65" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="M65" t="n">
         <v>0.61</v>
       </c>
       <c r="N65" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="O65" t="n">
         <v>-3.49</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.03</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45979.38541666666</v>
+        <v>45979.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>755.9</v>
+        <v>749.1</v>
       </c>
       <c r="I66" t="n">
         <v>753.4438608519119</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.79</v>
+        <v>-1.68</v>
       </c>
       <c r="L66" t="n">
         <v>2.58</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>4.48</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46024.55208333334</v>
+        <v>46027.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>698.7</v>
+        <v>709.8</v>
       </c>
       <c r="I67" t="n">
         <v>701.6520481330667</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>45</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>6.73</v>
+        <v>5.25</v>
       </c>
       <c r="L67" t="n">
         <v>1.29</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>4.61</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>691.4</v>
+        <v>677.45</v>
       </c>
       <c r="I68" t="n">
         <v>682.4964616420108</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.59</v>
+        <v>-4.56</v>
       </c>
       <c r="L68" t="n">
-        <v>2.79</v>
+        <v>5.16</v>
       </c>
       <c r="M68" t="n">
         <v>0.11</v>
       </c>
       <c r="N68" t="n">
-        <v>1.67</v>
+        <v>2.95</v>
       </c>
       <c r="O68" t="n">
         <v>1.9</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>5.98</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46050.55208333334</v>
+        <v>46051.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>626.4</v>
+        <v>638</v>
       </c>
       <c r="I69" t="n">
         <v>633.4190951770961</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K69" t="n">
-        <v>7.54</v>
+        <v>5.82</v>
       </c>
       <c r="L69" t="n">
         <v>2.41</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.81</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46066.38541666666</v>
+        <v>46066.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>636</v>
+        <v>626.8</v>
       </c>
       <c r="I70" t="n">
         <v>634.9027702709968</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.31</v>
+        <v>-1.76</v>
       </c>
       <c r="L70" t="n">
         <v>7.07</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>6.97</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>536</v>
+        <v>570</v>
       </c>
       <c r="I71" t="n">
         <v>542.1976930022289</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>53</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K71" t="n">
-        <v>14.49</v>
+        <v>9.06</v>
       </c>
       <c r="L71" t="n">
         <v>2.96</v>
       </c>
       <c r="M71" t="n">
-        <v>3.22</v>
+        <v>3.54</v>
       </c>
       <c r="N71" t="n">
-        <v>3.31</v>
+        <v>6.88</v>
       </c>
       <c r="O71" t="n">
         <v>-3.65</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>590.1</v>
+        <v>574.35</v>
       </c>
       <c r="I72" t="n">
         <v>586.3578449929191</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K72" t="n">
-        <v>3.53</v>
+        <v>0.76</v>
       </c>
       <c r="L72" t="n">
         <v>4.21</v>
@@ -4545,7 +5408,7 @@
         <v>2.91</v>
       </c>
       <c r="N72" t="n">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="O72" t="n">
         <v>6.88</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>7.23</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>586.45</v>
+        <v>615.05</v>
       </c>
       <c r="I73" t="n">
         <v>592.4291177497695</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K73" t="n">
-        <v>-2.11</v>
+        <v>-7.09</v>
       </c>
       <c r="L73" t="n">
-        <v>5.84</v>
+        <v>7.41</v>
       </c>
       <c r="M73" t="n">
-        <v>1.38</v>
+        <v>2.48</v>
       </c>
       <c r="N73" t="n">
-        <v>3.93</v>
+        <v>4.94</v>
       </c>
       <c r="O73" t="n">
         <v>-3.14</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>7.95</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>652.35</v>
+        <v>633</v>
       </c>
       <c r="I74" t="n">
         <v>641.9167244536351</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K74" t="n">
-        <v>6.06</v>
+        <v>2.92</v>
       </c>
       <c r="L74" t="n">
         <v>2.72</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>7.82</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46212.55208333334</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>657.95</v>
+        <v>687.75</v>
       </c>
       <c r="I75" t="n">
         <v>682.5184626273731</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.94</v>
+        <v>-8.65</v>
       </c>
       <c r="L75" t="n">
-        <v>5.21</v>
+        <v>9.32</v>
       </c>
       <c r="M75" t="n">
-        <v>0.66</v>
+        <v>1.83</v>
       </c>
       <c r="N75" t="n">
-        <v>3.94</v>
+        <v>4.57</v>
       </c>
       <c r="O75" t="n">
         <v>-2.89</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>9.49</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46274.55208333334</v>
+        <v>46275.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>659</v>
+        <v>657.8</v>
       </c>
       <c r="I76" t="n">
         <v>657.831341063084</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.18</v>
+        <v>-4.35</v>
       </c>
       <c r="L76" t="n">
         <v>8.31</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>4.33</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46283.55208333334</v>
+        <v>46286.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>651</v>
+        <v>656.3</v>
       </c>
       <c r="I77" t="n">
         <v>655.2062702600699</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K77" t="n">
-        <v>1.03</v>
+        <v>0.23</v>
       </c>
       <c r="L77" t="n">
         <v>0.7</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>5.9</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46302.55208333334</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>654.5</v>
+        <v>640.45</v>
       </c>
       <c r="I78" t="n">
         <v>649.1494747981925</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.27</v>
+        <v>-2.42</v>
       </c>
       <c r="L78" t="n">
-        <v>1.87</v>
+        <v>2.64</v>
       </c>
       <c r="M78" t="n">
         <v>1.22</v>
       </c>
       <c r="N78" t="n">
-        <v>2.26</v>
+        <v>2.59</v>
       </c>
       <c r="O78" t="n">
         <v>1.42</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>6.13</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>665</v>
+        <v>672.45</v>
       </c>
       <c r="I79" t="n">
         <v>669.5436333525474</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K79" t="n">
-        <v>-3.83</v>
+        <v>-5</v>
       </c>
       <c r="L79" t="n">
         <v>5.78</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -5004,6 +5963,12 @@
       <c r="Q80" t="n">
         <v>16</v>
       </c>
+      <c r="R80" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7106,7 +8071,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="6">
@@ -7116,7 +8081,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -7126,7 +8091,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82.2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -7136,7 +8101,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7146,7 +8111,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.2</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="10">
@@ -7156,7 +8121,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="11">
@@ -7196,7 +8161,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.81</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="15">
@@ -7206,7 +8171,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.89</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="16">
@@ -7216,7 +8181,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.72</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="17">
@@ -7226,7 +8191,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>40.52</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="18">
@@ -7236,7 +8201,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.4</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="19">
@@ -7246,7 +8211,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.89</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="20">
@@ -7256,7 +8221,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.44</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="21">
@@ -7266,7 +8231,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.39</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="22">
@@ -7276,7 +8241,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -7286,7 +8251,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -7296,7 +8261,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="25">
@@ -7316,7 +8281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.17</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="27">
@@ -7326,7 +8291,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.199999999999999</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="28">
@@ -7336,7 +8301,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
